--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.76495156580924</v>
+        <v>5.161804629444003</v>
       </c>
       <c r="D2" t="n">
-        <v>24.50442073522353</v>
+        <v>3.981968369473824</v>
       </c>
       <c r="E2" t="n">
-        <v>16.43363921123614</v>
+        <v>2.670466371825873</v>
       </c>
       <c r="F2" t="n">
-        <v>23.2868302383154</v>
+        <v>3.784109913726252</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.46846240767383</v>
+        <v>6.088625141246998</v>
       </c>
       <c r="D3" t="n">
-        <v>37.7424827910789</v>
+        <v>6.133153453550321</v>
       </c>
       <c r="E3" t="n">
-        <v>16.43363921123614</v>
+        <v>2.670466371825873</v>
       </c>
       <c r="F3" t="n">
-        <v>23.2868302383154</v>
+        <v>3.784109913726252</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.84322511420339</v>
+        <v>6.799524081058052</v>
       </c>
       <c r="D4" t="n">
-        <v>42.93752540218873</v>
+        <v>6.977347877855668</v>
       </c>
       <c r="E4" t="n">
-        <v>16.43363921123614</v>
+        <v>2.670466371825873</v>
       </c>
       <c r="F4" t="n">
-        <v>23.2868302383154</v>
+        <v>3.784109913726252</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.95477910109746</v>
+        <v>5.192651603928338</v>
       </c>
       <c r="D5" t="n">
-        <v>30.74382960779991</v>
+        <v>4.995872311267486</v>
       </c>
       <c r="E5" t="n">
-        <v>16.43363921123614</v>
+        <v>2.670466371825873</v>
       </c>
       <c r="F5" t="n">
-        <v>23.2868302383154</v>
+        <v>3.784109913726252</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>76.00694057088504</v>
+        <v>12.35112784276882</v>
       </c>
       <c r="D6" t="n">
-        <v>92.05948464129818</v>
+        <v>14.95966625421095</v>
       </c>
       <c r="E6" t="n">
-        <v>16.43363921123614</v>
+        <v>2.670466371825873</v>
       </c>
       <c r="F6" t="n">
-        <v>23.2868302383154</v>
+        <v>3.784109913726252</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.34807469476211</v>
+        <v>4.281562137898844</v>
       </c>
       <c r="D7" t="n">
-        <v>24.79515027508038</v>
+        <v>4.029211919700561</v>
       </c>
       <c r="E7" t="n">
-        <v>16.43363921123614</v>
+        <v>2.670466371825873</v>
       </c>
       <c r="F7" t="n">
-        <v>23.2868302383154</v>
+        <v>3.784109913726252</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
